--- a/LDC.xlsx
+++ b/LDC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/Regional-Economy-GGP-Sumsel-2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{2DAED9DC-B120-4F90-98C2-D54E44AB3033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4404E43D-269A-4D2A-914D-B5AEDF4B869E}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{2DAED9DC-B120-4F90-98C2-D54E44AB3033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56C05A52-698F-4EAD-89A9-CECF7CD2DD2A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C9587FB8-FD86-4834-AF5A-A903D591AACF}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{C9587FB8-FD86-4834-AF5A-A903D591AACF}"/>
   </bookViews>
   <sheets>
     <sheet name="LDC" sheetId="1" r:id="rId1"/>
@@ -770,7 +770,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="1">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -936,7 +936,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F10">
         <v>0.03</v>

--- a/LDC.xlsx
+++ b/LDC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/Regional-Economy-GGP-Sumsel-2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{2DAED9DC-B120-4F90-98C2-D54E44AB3033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56C05A52-698F-4EAD-89A9-CECF7CD2DD2A}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{2DAED9DC-B120-4F90-98C2-D54E44AB3033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88AC8B8E-B8B7-4366-88E1-52CEE67DD7E2}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{C9587FB8-FD86-4834-AF5A-A903D591AACF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C9587FB8-FD86-4834-AF5A-A903D591AACF}"/>
   </bookViews>
   <sheets>
     <sheet name="LDC" sheetId="1" r:id="rId1"/>
@@ -616,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J2" s="1">
         <v>0</v>
@@ -699,7 +699,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J3" s="1">
         <v>0</v>
@@ -770,7 +770,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="1">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -936,7 +936,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -1194,10 +1194,10 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I9" s="1">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J9" s="1">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F10">
         <v>0.03</v>
@@ -5086,7 +5086,7 @@
         <v>1</v>
       </c>
       <c r="E56">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="F56">
         <v>0.97</v>
@@ -5095,10 +5095,10 @@
         <v>0.92999999999999994</v>
       </c>
       <c r="H56">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I56">
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="J56">
         <v>0</v>
